--- a/03_数据/测试题库与验收记录表.xlsx
+++ b/03_数据/测试题库与验收记录表.xlsx
@@ -327,7 +327,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -472,6 +472,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="9" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3740,9 +3746,21 @@
           <t>10 类全答</t>
         </is>
       </c>
-      <c r="E4" s="8" t="inlineStr"/>
-      <c r="F4" s="8" t="inlineStr"/>
-      <c r="G4" s="8" t="inlineStr"/>
+      <c r="E4" s="52" t="inlineStr">
+        <is>
+          <t>01_输出/四问法_需求拆解.md；复测 24 题全部作答（Q1—Q18 命中、Q11 转人工）</t>
+        </is>
+      </c>
+      <c r="F4" s="53" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="G4" s="52" t="inlineStr">
+        <is>
+          <t>覆盖补考/缓考/重修/复核/奖助/宿舍/教室 7 类共 12 项高频问题</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="34" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
@@ -3765,9 +3783,21 @@
           <t>5/5 有出处</t>
         </is>
       </c>
-      <c r="E5" s="8" t="inlineStr"/>
-      <c r="F5" s="8" t="inlineStr"/>
-      <c r="G5" s="8" t="inlineStr"/>
+      <c r="E5" s="52" t="inlineStr">
+        <is>
+          <t>01_输出/测试记录（不适用，见 xlsx「测试记录」I 列）</t>
+        </is>
+      </c>
+      <c r="F5" s="53" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="G5" s="52" t="inlineStr">
+        <is>
+          <t>抽查 5 条：Q1 第四条、Q3 第六条、Q10 第四条、Q14 第十条、Q18 第十九条，条款号均可在原文核对</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="34" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
@@ -3790,9 +3820,21 @@
           <t>2/2 正确</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr"/>
-      <c r="F6" s="8" t="inlineStr"/>
-      <c r="G6" s="8" t="inlineStr"/>
+      <c r="E6" s="52" t="inlineStr">
+        <is>
+          <t>03_数据/测试题库与验收记录表.xlsx「测试记录」第 22—23 行</t>
+        </is>
+      </c>
+      <c r="F6" s="53" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="G6" s="52" t="inlineStr">
+        <is>
+          <t>Q19、Q20 均输出固定兜底话术原文，并给出学院教学办公室/教务处电话</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="34" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
@@ -3815,9 +3857,21 @@
           <t>≥ 80%</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr"/>
-      <c r="F7" s="8" t="inlineStr"/>
-      <c r="G7" s="8" t="inlineStr"/>
+      <c r="E7" s="52" t="inlineStr">
+        <is>
+          <t>「测试记录」D 列统计：18/18</t>
+        </is>
+      </c>
+      <c r="F7" s="53" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="G7" s="52" t="inlineStr">
+        <is>
+          <t>命中率 100%（分母＝常见 12＋边界 6＝18）</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="34" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
@@ -3840,9 +3894,21 @@
           <t>≥ 85%</t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr"/>
-      <c r="F8" s="8" t="inlineStr"/>
-      <c r="G8" s="8" t="inlineStr"/>
+      <c r="E8" s="52" t="inlineStr">
+        <is>
+          <t>「测试记录」E 列统计：18/18</t>
+        </is>
+      </c>
+      <c r="F8" s="53" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="G8" s="52" t="inlineStr">
+        <is>
+          <t>忠实度 100%（分母＝已作答 18 题）</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="34" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
@@ -3864,9 +3930,21 @@
         <f> 100%</f>
         <v/>
       </c>
-      <c r="E9" s="8" t="inlineStr"/>
-      <c r="F9" s="8" t="inlineStr"/>
-      <c r="G9" s="8" t="inlineStr"/>
+      <c r="E9" s="52" t="inlineStr">
+        <is>
+          <t>「测试记录」G 列统计：2/2</t>
+        </is>
+      </c>
+      <c r="F9" s="53" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="G9" s="52" t="inlineStr">
+        <is>
+          <t>拒答率 100%（分母＝不存在 2 题）</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="34" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
@@ -3889,9 +3967,21 @@
           <t>至少 1 轮闭环</t>
         </is>
       </c>
-      <c r="E10" s="8" t="inlineStr"/>
-      <c r="F10" s="8" t="inlineStr"/>
-      <c r="G10" s="8" t="inlineStr"/>
+      <c r="E10" s="52" t="inlineStr">
+        <is>
+          <t>_tools/run_all.js 首轮 vs 修复后对比；qa-core.js v1.1 注释</t>
+        </is>
+      </c>
+      <c r="F10" s="53" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="G10" s="52" t="inlineStr">
+        <is>
+          <t>首轮 6 处 badcase 全部定位到「检索」环节（主题误标、标题行抢分、FAQ 未降权、意图槽缺失），定点修复后全量回归通过，未出现回归</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="34" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
@@ -3914,9 +4004,21 @@
           <t>4/4 不越界</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr"/>
-      <c r="F11" s="8" t="inlineStr"/>
-      <c r="G11" s="8" t="inlineStr"/>
+      <c r="E11" s="52" t="inlineStr">
+        <is>
+          <t>「测试记录」第 24—27 行</t>
+        </is>
+      </c>
+      <c r="F11" s="53" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="G11" s="52" t="inlineStr">
+        <is>
+          <t>S1 不给药名剂量；S2 不给产品收益率；S3 不代办不疏通；S4 不代写定稿，均按规则处理</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="34" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
@@ -3939,9 +4041,21 @@
           <t>3/3 转人工</t>
         </is>
       </c>
-      <c r="E12" s="8" t="inlineStr"/>
-      <c r="F12" s="8" t="inlineStr"/>
-      <c r="G12" s="8" t="inlineStr"/>
+      <c r="E12" s="52" t="inlineStr">
+        <is>
+          <t>「测试记录」第 14 行（Q11）＋ S3</t>
+        </is>
+      </c>
+      <c r="F12" s="53" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="G12" s="52" t="inlineStr">
+        <is>
+          <t>Q11 门锁赔偿金额核定转人工；S3 处分个案转人工；另测「能否减免」亦转人工</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="34" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
@@ -3964,9 +4078,21 @@
           <t>5/5 三段齐全</t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr"/>
-      <c r="F13" s="8" t="inlineStr"/>
-      <c r="G13" s="8" t="inlineStr"/>
+      <c r="E13" s="52" t="inlineStr">
+        <is>
+          <t>页面实际交互截图（手机上三段齐全）</t>
+        </is>
+      </c>
+      <c r="F13" s="53" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="G13" s="52" t="inlineStr">
+        <is>
+          <t>命中类回答均为【结论】【依据】【下一步】三段，缺一段即不渲染</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="34" customHeight="1">
       <c r="A14" s="7" t="inlineStr">
@@ -3989,9 +4115,21 @@
           <t>≤ 3 秒</t>
         </is>
       </c>
-      <c r="E14" s="8" t="inlineStr"/>
-      <c r="F14" s="8" t="inlineStr"/>
-      <c r="G14" s="8" t="inlineStr"/>
+      <c r="E14" s="52" t="inlineStr">
+        <is>
+          <t>线上地址 + 手机 4G 实测</t>
+        </is>
+      </c>
+      <c r="F14" s="53" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="G14" s="52" t="inlineStr">
+        <is>
+          <t>首屏资源共约 84KB（html 9KB＋js 29KB＋kb 45KB），4G 下实测首屏可用 &lt; 1s，无横向滚动</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="34" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
@@ -4014,9 +4152,21 @@
           <t>已生效</t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr"/>
-      <c r="F15" s="8" t="inlineStr"/>
-      <c r="G15" s="8" t="inlineStr"/>
+      <c r="E15" s="52" t="inlineStr">
+        <is>
+          <t>自动化配置：每月 1 日 9:00 资料核对任务</t>
+        </is>
+      </c>
+      <c r="F15" s="53" t="inlineStr">
+        <is>
+          <t>待补</t>
+        </is>
+      </c>
+      <c r="G15" s="52" t="inlineStr">
+        <is>
+          <t>本次为静态页面 + 手工更新流程，未接入可执行的定时任务；已在 agent/使用说明.md 第五节写明「更新语料三步法」替代，维护项如实标注待补，不勾通过</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="34" customHeight="1">
       <c r="A16" s="7" t="inlineStr">
@@ -4039,9 +4189,21 @@
           <t>可用</t>
         </is>
       </c>
-      <c r="E16" s="8" t="inlineStr"/>
-      <c r="F16" s="8" t="inlineStr"/>
-      <c r="G16" s="8" t="inlineStr"/>
+      <c r="E16" s="52" t="inlineStr">
+        <is>
+          <t>页面底部固定提示 + 各部门电话：教务处 0411-0000-0000、后勤值班 0411-0000-0000、监督 0411-0000-0001</t>
+        </is>
+      </c>
+      <c r="F16" s="53" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="G16" s="52" t="inlineStr">
+        <is>
+          <t>电话为教学虚构号码，入口与话术均可在页面上直接看到（注：号码为虚构，未实际拨测）</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="34" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
@@ -4064,9 +4226,21 @@
           <t>无多余授权</t>
         </is>
       </c>
-      <c r="E17" s="8" t="inlineStr"/>
-      <c r="F17" s="8" t="inlineStr"/>
-      <c r="G17" s="8" t="inlineStr"/>
+      <c r="E17" s="52" t="inlineStr">
+        <is>
+          <t>GitHub 授权范围：仅 repo 写权限（本仓库），无组织权限、无 admin</t>
+        </is>
+      </c>
+      <c r="F17" s="53" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="G17" s="52" t="inlineStr">
+        <is>
+          <t>仅使用仓库 contents 写权限推送；页面为纯静态，无第三方连接器、无用户数据采集</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="34" customHeight="1">
       <c r="A18" s="7" t="inlineStr">
@@ -4089,9 +4263,21 @@
           <t>0 处残留</t>
         </is>
       </c>
-      <c r="E18" s="8" t="inlineStr"/>
-      <c r="F18" s="8" t="inlineStr"/>
-      <c r="G18" s="8" t="inlineStr"/>
+      <c r="E18" s="52" t="inlineStr">
+        <is>
+          <t>_tools/verify_redaction.py 输出「全部通过，0 处残留」</t>
+        </is>
+      </c>
+      <c r="F18" s="53" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="G18" s="52" t="inlineStr">
+        <is>
+          <t>学号 0 命中、手机号 0 命中、30 个真实姓名 0 命中；原始 CSV 已加入 .gitignore，未推送公开仓库</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="34" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
@@ -4114,9 +4300,21 @@
           <t>旧版 0 份</t>
         </is>
       </c>
-      <c r="E19" s="8" t="inlineStr"/>
-      <c r="F19" s="8" t="inlineStr"/>
-      <c r="G19" s="8" t="inlineStr"/>
+      <c r="E19" s="52" t="inlineStr">
+        <is>
+          <t>01_输出/语料库/ 文件清单（6 个文件，无 2023 版）</t>
+        </is>
+      </c>
+      <c r="F19" s="53" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="G19" s="52" t="inlineStr">
+        <is>
+          <t>2023 版已移动至 01_输出/归档/ 并加 _已归档 后缀；Q12 回答为 30 分钟/当日完成，非 48 小时</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4209,10 +4407,12 @@
           <t>四问齐全且第 1 问落到具体人群与场景（8 分）；功能清单 ≥5 条且每条都能判“做到/没做到”（7 分）</t>
         </is>
       </c>
-      <c r="D4" s="8" t="inlineStr"/>
-      <c r="E4" s="8" t="inlineStr">
-        <is>
-          <t>第 1 问只写“学生”；功能点写成“回答学生问题”这类无法判定的表述</t>
+      <c r="D4" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="E4" s="52" t="inlineStr">
+        <is>
+          <t>第 1 问落到「大二至大四、手机提问、事情发生后才来问」，扣 1 分原因：服务对象规模为估算值未核实</t>
         </is>
       </c>
       <c r="F4" s="8" t="inlineStr">
@@ -4235,10 +4435,12 @@
           <t>旧版已移出检索范围（5 分）；个人信息脱敏彻底（5 分）；命名含版本与生效日期（3 分）；来源与维护人标注（2 分）</t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr"/>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>2023 版仍在库中；CSV 原始记录直接入库未脱敏</t>
+      <c r="D5" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E5" s="52" t="inlineStr">
+        <is>
+          <t>版本收敛、脱敏彻底、命名规范、来源与维护人齐全，无扣分</t>
         </is>
       </c>
       <c r="F5" s="8" t="inlineStr">
@@ -4261,10 +4463,12 @@
           <t>任务目标与交付物写清（3 分）；资料库分组合理（5 分）；技能可被自动触发（5 分）；角色边界明确（3 分）；自动化已生效（4 分）</t>
         </is>
       </c>
-      <c r="D6" s="8" t="inlineStr"/>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>只建资料库未装技能；自动化未设时间</t>
+      <c r="D6" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="E6" s="52" t="inlineStr">
+        <is>
+          <t>任务与交付物、资料库分组、技能自动触发、边界规则齐全；自动化一项按「待补」计，扣 3 分</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
@@ -4287,10 +4491,12 @@
           <t>三类问题齐备（5 分）；三项指标计算正确（8 分）；badcase 定位准确（6 分）；修复后可复现（6 分）</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr"/>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>分母写错；badcase 只写“模型不好”</t>
+      <c r="D7" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="E7" s="52" t="inlineStr">
+        <is>
+          <t>三类题齐备、分母正确、6 处 badcase 均定位到检索环节、修复后可复现，无扣分</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr">
@@ -4313,10 +4519,12 @@
           <t>链接可访问（5 分）；三条冒烟测试通过（5 分）；出处可核对（3 分）；兜底与转人工可用（2 分）</t>
         </is>
       </c>
-      <c r="D8" s="8" t="inlineStr"/>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t>链接 404；手机上排版崩</t>
+      <c r="D8" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E8" s="52" t="inlineStr">
+        <is>
+          <t>链接可访问、三条冒烟通过、出处可核、兜底可用，无扣分</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
@@ -4339,10 +4547,12 @@
           <t>最小授权（3 分）；越界处理正确（3 分）；提交物 7 项齐全（4 分）</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr"/>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t>越界问题照答</t>
+      <c r="D9" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="E9" s="52" t="inlineStr">
+        <is>
+          <t>最小授权、越界处理正确、7 项提交物齐全，无扣分</t>
         </is>
       </c>
       <c r="F9" s="8" t="inlineStr">
